--- a/outputs/plan.xlsx
+++ b/outputs/plan.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +17,23 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +56,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,13 +429,535 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Placeholder - demand plan to be generated by src/newsvendor.py</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Demand uplift by country and scenario (basketball category, vs. baseline plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>k = 0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Own event</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.06533853931086002</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.07650039615825997</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.051794368694995</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.06533853931086002</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.07650039615825997</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.051794368694995</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.06533853931086002</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.07650039615825997</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.051794368694995</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.06533853931086002</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.07650039615825997</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.051794368694995</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B9" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.06533853931086002</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.07650039615825997</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.051794368694995</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.06533853931086002</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.07650039615825997</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.051794368694995</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>k = 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Own event</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.13067707862172</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.1530007923165199</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.10358873738999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.13067707862172</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.1530007923165199</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.10358873738999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.13067707862172</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.1530007923165199</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.10358873738999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.13067707862172</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.1530007923165199</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.10358873738999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B18" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.13067707862172</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.1530007923165199</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.10358873738999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B19" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.13067707862172</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.1530007923165199</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.10358873738999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Low scenario source</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nba_paris_2025 (France): 0.0% (floored from -11.2%)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Weakest-performing NBA game; net uplift was negative, so it's floored at 0% (see floor rule below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Base scenario source</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nba_berlin_2026 (Germany): 26.1%</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Middle-performing NBA game; used as the base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>High scenario source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nba_london_2026 (UK): 30.6%</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Best-performing NBA game; used as the upside case</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Negative value floor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>A league is unlikely to reduce category demand, so a negative net uplift is treated as no effect, not a decline</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Interest-to-demand conversion (k)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.25 and 0.5</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Share of extra Wikipedia interest assumed to convert to extra purchases; no public data exists, so two values are tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Scenario probabilities</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>low 25%, base 50%, high 25%</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Judgement call, not derived from data; weights the three NBA games into one expected case</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Same numbers for all countries</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UK, France, Spain, Italy, Germany, Turkey</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Only 3 of 6 markets have their own measured game; the data supports a shared European uplift, not country-by-country differences</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Netherlands excluded</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>No planned NBA franchise, so not part of the demand plan</t>
         </is>
       </c>
     </row>

--- a/outputs/plan.xlsx
+++ b/outputs/plan.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Buy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -55,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,4 +547,205 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Buy recommendation (newsvendor: Cu = gross margin, Co = markdown depth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross margin (Cu)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FY2025 (ended 2025-05-31) -- Nike 10-K FY2025: https://www.sec.gov/Archives/edgar/data/320187/000032018725000047/nke-20250531.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Markdown depth (Co)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30% and 50%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tested at two depths; a deeper markdown lowers the critical ratio and pushes the buy down</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cumulative probability</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>low 40%, base 80%, high 100%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>From scenarios.csv's low/base/high probabilities (40/40/20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Markdown</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Critical ratio</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Recommended scenario</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Buy (% above plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0.5873452544704264</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.06533853931086001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.4606256742179072</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.06533853931086001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.5873452544704264</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.13067707862172</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.4606256742179072</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.13067707862172</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Buy = the scenario level that balances missed full-price sales against markdown losses.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>